--- a/data/base/Backlog_43.xlsx
+++ b/data/base/Backlog_43.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\Base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C121530-1194-4CD1-B40D-478F28DE7C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F9F2E6-3474-473A-AD6A-507459057804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -106,9 +106,6 @@
     <t>Lourival Silva</t>
   </si>
   <si>
-    <t>Erick Silva</t>
-  </si>
-  <si>
     <t>Gabriel López</t>
   </si>
   <si>
@@ -134,6 +131,9 @@
   </si>
   <si>
     <t>Eduardo da Silva</t>
+  </si>
+  <si>
+    <t>Erick da Silva</t>
   </si>
 </sst>
 </file>
@@ -716,7 +716,7 @@
         <v>45957</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>14</v>
@@ -755,7 +755,7 @@
         <v>45957</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>14</v>
@@ -794,7 +794,7 @@
         <v>45957</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>14</v>
@@ -833,7 +833,7 @@
         <v>45957</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>14</v>
@@ -848,7 +848,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="8">
         <v>2025</v>
@@ -872,7 +872,7 @@
         <v>45957</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>14</v>
@@ -968,7 +968,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C9" s="8">
         <v>2025</v>
@@ -1010,7 +1010,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C10" s="8">
         <v>2025</v>
@@ -1052,7 +1052,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C11" s="8">
         <v>2025</v>
@@ -1076,7 +1076,7 @@
         <v>45957</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>14</v>
@@ -1091,7 +1091,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="8">
         <v>2025</v>
@@ -1130,7 +1130,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="8">
         <v>2025</v>
@@ -1154,7 +1154,7 @@
         <v>45957</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>14</v>
@@ -1169,7 +1169,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="8">
         <v>2025</v>
@@ -1193,7 +1193,7 @@
         <v>45957</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>14</v>
@@ -1208,7 +1208,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="8">
         <v>2025</v>
@@ -1232,7 +1232,7 @@
         <v>45957</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>14</v>
@@ -1247,7 +1247,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="8">
         <v>2025</v>
@@ -1271,7 +1271,7 @@
         <v>45957</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>14</v>
@@ -1427,7 +1427,7 @@
         <v>45957</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>14</v>
@@ -1466,7 +1466,7 @@
         <v>45957</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>14</v>
@@ -1505,7 +1505,7 @@
         <v>45957</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>14</v>
@@ -1544,7 +1544,7 @@
         <v>45957</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>14</v>
@@ -1598,7 +1598,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="8">
         <v>2025</v>
@@ -1622,7 +1622,7 @@
         <v>45957</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>14</v>
@@ -1637,7 +1637,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" s="8">
         <v>2025</v>
@@ -1676,7 +1676,7 @@
         <v>11</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27" s="8">
         <v>2025</v>
@@ -1700,7 +1700,7 @@
         <v>45957</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>14</v>
@@ -1739,7 +1739,7 @@
         <v>45957</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>14</v>
@@ -1778,7 +1778,7 @@
         <v>45957</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>14</v>
@@ -1879,7 +1879,7 @@
         <v>18</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="16">
         <v>2025</v>
@@ -1903,7 +1903,7 @@
         <v>45957</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K2" s="16" t="s">
         <v>19</v>
@@ -1914,7 +1914,7 @@
         <v>18</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="16">
         <v>2025</v>
@@ -1938,7 +1938,7 @@
         <v>45957</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K3" s="16" t="s">
         <v>19</v>
@@ -1949,7 +1949,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="16">
         <v>2025</v>
@@ -1973,7 +1973,7 @@
         <v>45957</v>
       </c>
       <c r="J4" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K4" s="16" t="s">
         <v>19</v>
@@ -1984,7 +1984,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="16">
         <v>2025</v>
@@ -2008,7 +2008,7 @@
         <v>45957</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>19</v>
@@ -2019,7 +2019,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="16">
         <v>2025</v>
@@ -2043,7 +2043,7 @@
         <v>45957</v>
       </c>
       <c r="J6" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>19</v>
@@ -2054,7 +2054,7 @@
         <v>18</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="16">
         <v>2025</v>
@@ -2078,7 +2078,7 @@
         <v>45957</v>
       </c>
       <c r="J7" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>19</v>
